--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3141"/>
+  <dimension ref="A1:C3142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53813,6 +53813,23 @@
         </is>
       </c>
     </row>
+    <row r="3142">
+      <c r="A3142" t="inlineStr">
+        <is>
+          <t>CVE-2026-51990</t>
+        </is>
+      </c>
+      <c r="B3142" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C3142" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-exploit-tencent-app-flaw-to-deploy-grayrabbit-malware/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3142"/>
+  <dimension ref="A1:C3145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53830,6 +53830,57 @@
         </is>
       </c>
     </row>
+    <row r="3143">
+      <c r="A3143" t="inlineStr">
+        <is>
+          <t>CVE-2021-22175</t>
+        </is>
+      </c>
+      <c r="B3143" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3143" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-hackers-now-exploit-max-severity-gitlab-flaw-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="inlineStr">
+        <is>
+          <t>CVE-2021-39935</t>
+        </is>
+      </c>
+      <c r="B3144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3144" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-hackers-now-exploit-max-severity-gitlab-flaw-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="inlineStr">
+        <is>
+          <t>CVE-2026-85706</t>
+        </is>
+      </c>
+      <c r="B3145" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3145" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-hackers-now-exploit-max-severity-gitlab-flaw-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3145"/>
+  <dimension ref="A1:C3149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53881,6 +53881,74 @@
         </is>
       </c>
     </row>
+    <row r="3146">
+      <c r="A3146" t="inlineStr">
+        <is>
+          <t>CVE-2025-31125</t>
+        </is>
+      </c>
+      <c r="B3146" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3146" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-target-exposed-vite-dev-servers-to-steal-aws-azure-secrets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="inlineStr">
+        <is>
+          <t>CVE-2024-45811</t>
+        </is>
+      </c>
+      <c r="B3147" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3147" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-target-exposed-vite-dev-servers-to-steal-aws-azure-secrets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="inlineStr">
+        <is>
+          <t>CVE-2025-30208</t>
+        </is>
+      </c>
+      <c r="B3148" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3148" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-target-exposed-vite-dev-servers-to-steal-aws-azure-secrets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="inlineStr">
+        <is>
+          <t>CVE-2026-39364</t>
+        </is>
+      </c>
+      <c r="B3149" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3149" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-target-exposed-vite-dev-servers-to-steal-aws-azure-secrets/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3149"/>
+  <dimension ref="A1:C3150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53949,6 +53949,23 @@
         </is>
       </c>
     </row>
+    <row r="3150">
+      <c r="A3150" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="B3150" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3150" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/japans-digital-agency-says-vpn-flaw-exposed-246-000-personnel-records/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3150"/>
+  <dimension ref="A1:C3157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53966,6 +53966,125 @@
         </is>
       </c>
     </row>
+    <row r="3151">
+      <c r="A3151" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="B3151" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3151" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="inlineStr">
+        <is>
+          <t>CVE-2026-76441</t>
+        </is>
+      </c>
+      <c r="B3152" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3152" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="inlineStr">
+        <is>
+          <t>CVE-2026-76443</t>
+        </is>
+      </c>
+      <c r="B3153" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3153" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="inlineStr">
+        <is>
+          <t>CVE-2026-76440</t>
+        </is>
+      </c>
+      <c r="B3154" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3154" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" t="inlineStr">
+        <is>
+          <t>CVE-2025-20393</t>
+        </is>
+      </c>
+      <c r="B3155" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3155" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="inlineStr">
+        <is>
+          <t>CVE-2026-76461</t>
+        </is>
+      </c>
+      <c r="B3156" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3156" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="inlineStr">
+        <is>
+          <t>CVE-2026-20353</t>
+        </is>
+      </c>
+      <c r="B3157" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3157" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-cisco-secure-email-zero-day-exploited-to-execute-commands-as-root/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3157"/>
+  <dimension ref="A1:C3162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54085,6 +54085,91 @@
         </is>
       </c>
     </row>
+    <row r="3158">
+      <c r="A3158" t="inlineStr">
+        <is>
+          <t>CVE-2025-60710</t>
+        </is>
+      </c>
+      <c r="B3158" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3158" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-critical-vmware-vcenter-rce-flaw-now-exploited-by-ransomware-gangs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" t="inlineStr">
+        <is>
+          <t>CVE-2026-22719</t>
+        </is>
+      </c>
+      <c r="B3159" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3159" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-critical-vmware-vcenter-rce-flaw-now-exploited-by-ransomware-gangs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="inlineStr">
+        <is>
+          <t>CVE-2025-22225</t>
+        </is>
+      </c>
+      <c r="B3160" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3160" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-critical-vmware-vcenter-rce-flaw-now-exploited-by-ransomware-gangs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="inlineStr">
+        <is>
+          <t>CVE-2024-37079</t>
+        </is>
+      </c>
+      <c r="B3161" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3161" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-critical-vmware-vcenter-rce-flaw-now-exploited-by-ransomware-gangs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="inlineStr">
+        <is>
+          <t>CVE-2026-59310</t>
+        </is>
+      </c>
+      <c r="B3162" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3162" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-critical-vmware-vcenter-rce-flaw-now-exploited-by-ransomware-gangs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3162"/>
+  <dimension ref="A1:C3163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54170,6 +54170,23 @@
         </is>
       </c>
     </row>
+    <row r="3163">
+      <c r="A3163" t="inlineStr">
+        <is>
+          <t>CVE-2026-1001</t>
+        </is>
+      </c>
+      <c r="B3163" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3163" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/what-zero-day-response-should-be-in-the-post-mythos-era/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3163"/>
+  <dimension ref="A1:C3164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54187,6 +54187,23 @@
         </is>
       </c>
     </row>
+    <row r="3164">
+      <c r="A3164" t="inlineStr">
+        <is>
+          <t>CVE-2026-27540</t>
+        </is>
+      </c>
+      <c r="B3164" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3164" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-target-wordpress-sites-via-third-party-woocommerce-plugin/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3164"/>
+  <dimension ref="A1:C3165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54204,6 +54204,23 @@
         </is>
       </c>
     </row>
+    <row r="3165">
+      <c r="A3165" t="inlineStr">
+        <is>
+          <t>CVE-2026-87886</t>
+        </is>
+      </c>
+      <c r="B3165" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3165" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/acronis-warns-of-actively-exploited-flaw-in-its-cpanel-backup-plugin/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3165"/>
+  <dimension ref="A1:C3167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54221,6 +54221,40 @@
         </is>
       </c>
     </row>
+    <row r="3166">
+      <c r="A3166" t="inlineStr">
+        <is>
+          <t>CVE-2026-58704</t>
+        </is>
+      </c>
+      <c r="B3166" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3166" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/google-fixes-actively-exploited-android-zero-day-on-pixel-devices/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" t="inlineStr">
+        <is>
+          <t>CVE-2025-48595</t>
+        </is>
+      </c>
+      <c r="B3167" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3167" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/google-fixes-actively-exploited-android-zero-day-on-pixel-devices/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3167"/>
+  <dimension ref="A1:C3171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54255,6 +54255,74 @@
         </is>
       </c>
     </row>
+    <row r="3168">
+      <c r="A3168" t="inlineStr">
+        <is>
+          <t>CVE-2026-84869</t>
+        </is>
+      </c>
+      <c r="B3168" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3168" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-hackers-exploiting-critical-screenconnect-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="inlineStr">
+        <is>
+          <t>CVE-2024-1709</t>
+        </is>
+      </c>
+      <c r="B3169" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3169" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-hackers-exploiting-critical-screenconnect-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" t="inlineStr">
+        <is>
+          <t>CVE-2026-3564</t>
+        </is>
+      </c>
+      <c r="B3170" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3170" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-hackers-exploiting-critical-screenconnect-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="inlineStr">
+        <is>
+          <t>CVE-2025-3935</t>
+        </is>
+      </c>
+      <c r="B3171" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3171" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-hackers-exploiting-critical-screenconnect-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3171"/>
+  <dimension ref="A1:C3178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54323,6 +54323,125 @@
         </is>
       </c>
     </row>
+    <row r="3172">
+      <c r="A3172" t="inlineStr">
+        <is>
+          <t>CVE-2025-20337</t>
+        </is>
+      </c>
+      <c r="B3172" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3172" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="inlineStr">
+        <is>
+          <t>CVE-2026-20284</t>
+        </is>
+      </c>
+      <c r="B3173" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3173" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="inlineStr">
+        <is>
+          <t>CVE-2026-76423</t>
+        </is>
+      </c>
+      <c r="B3174" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3174" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="inlineStr">
+        <is>
+          <t>CVE-2026-76460</t>
+        </is>
+      </c>
+      <c r="B3175" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3175" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="inlineStr">
+        <is>
+          <t>CVE-2026-20176</t>
+        </is>
+      </c>
+      <c r="B3176" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3176" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="inlineStr">
+        <is>
+          <t>CVE-2026-20211</t>
+        </is>
+      </c>
+      <c r="B3177" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3177" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="inlineStr">
+        <is>
+          <t>CVE-2026-20307</t>
+        </is>
+      </c>
+      <c r="B3178" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3178" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-identity-service-engine-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3178"/>
+  <dimension ref="A1:C3183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54442,6 +54442,91 @@
         </is>
       </c>
     </row>
+    <row r="3179">
+      <c r="A3179" t="inlineStr">
+        <is>
+          <t>CVE-2026-16232</t>
+        </is>
+      </c>
+      <c r="B3179" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3179" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-critical-flaw-lets-hackers-execute-code-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="inlineStr">
+        <is>
+          <t>CVE-2026-50751</t>
+        </is>
+      </c>
+      <c r="B3180" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3180" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-critical-flaw-lets-hackers-execute-code-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="inlineStr">
+        <is>
+          <t>CVE-2026-91843</t>
+        </is>
+      </c>
+      <c r="B3181" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3181" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-critical-flaw-lets-hackers-execute-code-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="inlineStr">
+        <is>
+          <t>CVE-2026-85103</t>
+        </is>
+      </c>
+      <c r="B3182" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3182" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-critical-flaw-lets-hackers-execute-code-as-root/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="inlineStr">
+        <is>
+          <t>CVE-2026-85102</t>
+        </is>
+      </c>
+      <c r="B3183" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3183" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-critical-flaw-lets-hackers-execute-code-as-root/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3183"/>
+  <dimension ref="A1:C3184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54527,6 +54527,23 @@
         </is>
       </c>
     </row>
+    <row r="3184">
+      <c r="A3184" t="inlineStr">
+        <is>
+          <t>CVE-2025-61882</t>
+        </is>
+      </c>
+      <c r="B3184" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C3184" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/shinyhunters-hacks-clop-leak-site-threatens-to-extort-ransomware-gang/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3184"/>
+  <dimension ref="A1:C3186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54544,6 +54544,40 @@
         </is>
       </c>
     </row>
+    <row r="3185">
+      <c r="A3185" t="inlineStr">
+        <is>
+          <t>CVE-2026-55945</t>
+        </is>
+      </c>
+      <c r="B3185" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C3185" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/bragjack-attacks-hijack-ai-browser-agents-through-malicious-extensions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="inlineStr">
+        <is>
+          <t>CVE-2026-0628</t>
+        </is>
+      </c>
+      <c r="B3186" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C3186" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/bragjack-attacks-hijack-ai-browser-agents-through-malicious-extensions/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3186"/>
+  <dimension ref="A1:C3189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54578,6 +54578,57 @@
         </is>
       </c>
     </row>
+    <row r="3187">
+      <c r="A3187" t="inlineStr">
+        <is>
+          <t>CVE-2025-39682</t>
+        </is>
+      </c>
+      <c r="B3187" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3187" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-alerts-of-active-exploitation-of-three-linux-kernel-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="inlineStr">
+        <is>
+          <t>CVE-2026-53266</t>
+        </is>
+      </c>
+      <c r="B3188" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3188" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-alerts-of-active-exploitation-of-three-linux-kernel-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="inlineStr">
+        <is>
+          <t>CVE-2025-39964</t>
+        </is>
+      </c>
+      <c r="B3189" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3189" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-alerts-of-active-exploitation-of-three-linux-kernel-flaws/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3189"/>
+  <dimension ref="A1:C3191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54629,6 +54629,40 @@
         </is>
       </c>
     </row>
+    <row r="3190">
+      <c r="A3190" t="inlineStr">
+        <is>
+          <t>CVE-2026-7273</t>
+        </is>
+      </c>
+      <c r="B3190" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3190" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-actively-exploited-zyxel-flaw-by-thursday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="inlineStr">
+        <is>
+          <t>CVE-2024-40891</t>
+        </is>
+      </c>
+      <c r="B3191" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3191" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-actively-exploited-zyxel-flaw-by-thursday/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3191"/>
+  <dimension ref="A1:C3193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54663,6 +54663,40 @@
         </is>
       </c>
     </row>
+    <row r="3192">
+      <c r="A3192" t="inlineStr">
+        <is>
+          <t>CVE-2026-86510</t>
+        </is>
+      </c>
+      <c r="B3192" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3192" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/d-link-warns-of-max-severity-zero-day-bug-in-dir-822a-routers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="inlineStr">
+        <is>
+          <t>CVE-2026-86296</t>
+        </is>
+      </c>
+      <c r="B3193" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3193" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/d-link-warns-of-max-severity-zero-day-bug-in-dir-822a-routers/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3193"/>
+  <dimension ref="A1:C3199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54697,6 +54697,108 @@
         </is>
       </c>
     </row>
+    <row r="3194">
+      <c r="A3194" t="inlineStr">
+        <is>
+          <t>CVE-2026-50751</t>
+        </is>
+      </c>
+      <c r="B3194" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3194" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="inlineStr">
+        <is>
+          <t>CVE-2026-16232</t>
+        </is>
+      </c>
+      <c r="B3195" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3195" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="inlineStr">
+        <is>
+          <t>CVE-2026-85103</t>
+        </is>
+      </c>
+      <c r="B3196" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3196" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="inlineStr">
+        <is>
+          <t>CVE-2024-24919</t>
+        </is>
+      </c>
+      <c r="B3197" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3197" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="inlineStr">
+        <is>
+          <t>CVE-2026-93616</t>
+        </is>
+      </c>
+      <c r="B3198" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3198" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="inlineStr">
+        <is>
+          <t>CVE-2026-85102</t>
+        </is>
+      </c>
+      <c r="B3199" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3199" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-patches-management-server-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3199"/>
+  <dimension ref="A1:C3211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54799,6 +54799,210 @@
         </is>
       </c>
     </row>
+    <row r="3200">
+      <c r="A3200" t="inlineStr">
+        <is>
+          <t>CVE-2026-60137</t>
+        </is>
+      </c>
+      <c r="B3200" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3200" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="inlineStr">
+        <is>
+          <t>CVE-2023-54391</t>
+        </is>
+      </c>
+      <c r="B3201" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3201" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="inlineStr">
+        <is>
+          <t>CVE-2026-63030</t>
+        </is>
+      </c>
+      <c r="B3202" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3202" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="inlineStr">
+        <is>
+          <t>CVE-2026-56271</t>
+        </is>
+      </c>
+      <c r="B3203" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3203" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="inlineStr">
+        <is>
+          <t>CVE-2026-79756</t>
+        </is>
+      </c>
+      <c r="B3204" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3204" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="inlineStr">
+        <is>
+          <t>CVE-2026-34909</t>
+        </is>
+      </c>
+      <c r="B3205" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3205" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="inlineStr">
+        <is>
+          <t>CVE-2026-54569</t>
+        </is>
+      </c>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="inlineStr">
+        <is>
+          <t>CVE-2026-7273</t>
+        </is>
+      </c>
+      <c r="B3207" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3207" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="inlineStr">
+        <is>
+          <t>CVE-2026-34910</t>
+        </is>
+      </c>
+      <c r="B3208" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3208" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="inlineStr">
+        <is>
+          <t>CVE-2026-60004</t>
+        </is>
+      </c>
+      <c r="B3209" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3209" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="inlineStr">
+        <is>
+          <t>CVE-2026-34908</t>
+        </is>
+      </c>
+      <c r="B3210" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3210" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="inlineStr">
+        <is>
+          <t>CVE-2022-0847</t>
+        </is>
+      </c>
+      <c r="B3211" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3211" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/chinese-hackers-exploit-multiple-technologies-to-steal-govt-data/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3211"/>
+  <dimension ref="A1:C3212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55003,6 +55003,23 @@
         </is>
       </c>
     </row>
+    <row r="3212">
+      <c r="A3212" t="inlineStr">
+        <is>
+          <t>CVE-2026-94127</t>
+        </is>
+      </c>
+      <c r="B3212" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3212" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/f5-warns-of-big-ip-apm-remote-code-execution-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3212"/>
+  <dimension ref="A1:C3215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55020,6 +55020,57 @@
         </is>
       </c>
     </row>
+    <row r="3213">
+      <c r="A3213" t="inlineStr">
+        <is>
+          <t>CVE-2026-16812</t>
+        </is>
+      </c>
+      <c r="B3213" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3213" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/arista-patches-actively-exploited-velocloud-orchestrator-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="inlineStr">
+        <is>
+          <t>CVE-2026-7473</t>
+        </is>
+      </c>
+      <c r="B3214" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3214" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/arista-patches-actively-exploited-velocloud-orchestrator-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="inlineStr">
+        <is>
+          <t>CVE-2026-93952</t>
+        </is>
+      </c>
+      <c r="B3215" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3215" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/arista-patches-actively-exploited-velocloud-orchestrator-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3215"/>
+  <dimension ref="A1:C3230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55071,6 +55071,261 @@
         </is>
       </c>
     </row>
+    <row r="3216">
+      <c r="A3216" t="inlineStr">
+        <is>
+          <t>CVE-2026-20316</t>
+        </is>
+      </c>
+      <c r="B3216" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3216" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="B3217" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3217" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" t="inlineStr">
+        <is>
+          <t>CVE-2026-83548</t>
+        </is>
+      </c>
+      <c r="B3218" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3218" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" t="inlineStr">
+        <is>
+          <t>CVE-2026-85103</t>
+        </is>
+      </c>
+      <c r="B3219" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3219" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="inlineStr">
+        <is>
+          <t>CVE-2026-33197</t>
+        </is>
+      </c>
+      <c r="B3220" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3220" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="B3221" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3221" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="inlineStr">
+        <is>
+          <t>CVE-2026-31431</t>
+        </is>
+      </c>
+      <c r="B3222" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3222" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="inlineStr">
+        <is>
+          <t>CVE-2026-76460</t>
+        </is>
+      </c>
+      <c r="B3223" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3223" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="inlineStr">
+        <is>
+          <t>CVE-2026-73453</t>
+        </is>
+      </c>
+      <c r="B3224" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3224" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="inlineStr">
+        <is>
+          <t>CVE-2026-73456</t>
+        </is>
+      </c>
+      <c r="B3225" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3225" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="B3226" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3226" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="inlineStr">
+        <is>
+          <t>CVE-2026-6485</t>
+        </is>
+      </c>
+      <c r="B3227" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3227" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="inlineStr">
+        <is>
+          <t>CVE-2026-85102</t>
+        </is>
+      </c>
+      <c r="B3228" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3228" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="inlineStr">
+        <is>
+          <t>CVE-2026-83549</t>
+        </is>
+      </c>
+      <c r="B3229" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3229" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="inlineStr">
+        <is>
+          <t>CVE-2026-91843</t>
+        </is>
+      </c>
+      <c r="B3230" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3230" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/infratrust-report-warns-network-management-systems-under-attack/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3230"/>
+  <dimension ref="A1:C3231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55326,6 +55326,23 @@
         </is>
       </c>
     </row>
+    <row r="3231">
+      <c r="A3231" t="inlineStr">
+        <is>
+          <t>CVE-2026-87902</t>
+        </is>
+      </c>
+      <c r="B3231" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3231" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-start-exploiting-critical-wordpress-flaw-for-code-execution/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3231"/>
+  <dimension ref="A1:C3233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55343,6 +55343,40 @@
         </is>
       </c>
     </row>
+    <row r="3232">
+      <c r="A3232" t="inlineStr">
+        <is>
+          <t>CVE-2026-93616</t>
+        </is>
+      </c>
+      <c r="B3232" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3232" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-of-hackers-exploiting-security-gateway-vpn-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="inlineStr">
+        <is>
+          <t>CVE-2026-85102</t>
+        </is>
+      </c>
+      <c r="B3233" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3233" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/check-point-warns-of-hackers-exploiting-security-gateway-vpn-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3233"/>
+  <dimension ref="A1:C3234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55377,6 +55377,23 @@
         </is>
       </c>
     </row>
+    <row r="3234">
+      <c r="A3234" t="inlineStr">
+        <is>
+          <t>CVE-2026-63077</t>
+        </is>
+      </c>
+      <c r="B3234" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3234" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-ransomware-gangs-now-exploiting-critical-teamcity-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3234"/>
+  <dimension ref="A1:C3241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55394,6 +55394,125 @@
         </is>
       </c>
     </row>
+    <row r="3235">
+      <c r="A3235" t="inlineStr">
+        <is>
+          <t>CVE-2020-35730</t>
+        </is>
+      </c>
+      <c r="B3235" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3235" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="inlineStr">
+        <is>
+          <t>CVE-2021-44026</t>
+        </is>
+      </c>
+      <c r="B3236" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3236" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="inlineStr">
+        <is>
+          <t>CVE-2025-68461</t>
+        </is>
+      </c>
+      <c r="B3237" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3237" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="inlineStr">
+        <is>
+          <t>CVE-2020-12641</t>
+        </is>
+      </c>
+      <c r="B3238" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3238" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="inlineStr">
+        <is>
+          <t>CVE-2023-5631</t>
+        </is>
+      </c>
+      <c r="B3239" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3239" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="inlineStr">
+        <is>
+          <t>CVE-2026-48842</t>
+        </is>
+      </c>
+      <c r="B3240" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3240" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="inlineStr">
+        <is>
+          <t>CVE-2025-49113</t>
+        </is>
+      </c>
+      <c r="B3241" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3241" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/critical-roundcube-flaw-now-actively-exploited-in-code-injection-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3241"/>
+  <dimension ref="A1:C3245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55513,6 +55513,74 @@
         </is>
       </c>
     </row>
+    <row r="3242">
+      <c r="A3242" t="inlineStr">
+        <is>
+          <t>CVE-2026-67279</t>
+        </is>
+      </c>
+      <c r="B3242" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3242" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-sharepoint-wso2-adobe-commerce-flaws-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3243" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3243" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-sharepoint-wso2-adobe-commerce-flaws-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="inlineStr">
+        <is>
+          <t>CVE-2026-71362</t>
+        </is>
+      </c>
+      <c r="B3244" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3244" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-sharepoint-wso2-adobe-commerce-flaws-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="inlineStr">
+        <is>
+          <t>CVE-2026-5430</t>
+        </is>
+      </c>
+      <c r="B3245" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3245" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-sharepoint-wso2-adobe-commerce-flaws-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3245"/>
+  <dimension ref="A1:C3246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55581,6 +55581,23 @@
         </is>
       </c>
     </row>
+    <row r="3246">
+      <c r="A3246" t="inlineStr">
+        <is>
+          <t>CVE-2026-42608</t>
+        </is>
+      </c>
+      <c r="B3246" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3246" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/shinyhunters-hacked-clop-leak-site-using-grav-cms-path-traversal-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3246"/>
+  <dimension ref="A1:C3247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55598,6 +55598,23 @@
         </is>
       </c>
     </row>
+    <row r="3247">
+      <c r="A3247" t="inlineStr">
+        <is>
+          <t>CVE-2026-35273</t>
+        </is>
+      </c>
+      <c r="B3247" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C3247" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/shinyhunters-uses-waf-bypass-trick-in-oracle-peoplesoft-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3247"/>
+  <dimension ref="A1:C3249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55615,6 +55615,40 @@
         </is>
       </c>
     </row>
+    <row r="3248">
+      <c r="A3248" t="inlineStr">
+        <is>
+          <t>CVE-2026-19489</t>
+        </is>
+      </c>
+      <c r="B3248" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3248" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-admins-warned-to-shut-down-netscalers-over-2-exploited-zero-days/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="inlineStr">
+        <is>
+          <t>CVE-2026-19490</t>
+        </is>
+      </c>
+      <c r="B3249" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3249" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-admins-warned-to-shut-down-netscalers-over-2-exploited-zero-days/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3249"/>
+  <dimension ref="A1:C3251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55649,6 +55649,40 @@
         </is>
       </c>
     </row>
+    <row r="3250">
+      <c r="A3250" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3250" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3250" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-admins-warned-to-shut-down-netscalers-over-2-exploited-zero-days/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3251" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3251" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-admins-warned-to-shut-down-netscalers-over-2-exploited-zero-days/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3251"/>
+  <dimension ref="A1:C3256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55683,6 +55683,91 @@
         </is>
       </c>
     </row>
+    <row r="3252">
+      <c r="A3252" t="inlineStr">
+        <is>
+          <t>CVE-2026-19490</t>
+        </is>
+      </c>
+      <c r="B3252" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3252" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-exploited-citrix-flaws-by-wednesday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3253" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3253" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-exploited-citrix-flaws-by-wednesday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="inlineStr">
+        <is>
+          <t>CVE-2026-3055</t>
+        </is>
+      </c>
+      <c r="B3254" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3254" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-exploited-citrix-flaws-by-wednesday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="inlineStr">
+        <is>
+          <t>CVE-2026-4368</t>
+        </is>
+      </c>
+      <c r="B3255" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3255" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-exploited-citrix-flaws-by-wednesday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3256" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3256" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-orders-feds-to-patch-exploited-citrix-flaws-by-wednesday/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3256"/>
+  <dimension ref="A1:C3265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55768,6 +55768,159 @@
         </is>
       </c>
     </row>
+    <row r="3257">
+      <c r="A3257" t="inlineStr">
+        <is>
+          <t>CVE-2025-31200</t>
+        </is>
+      </c>
+      <c r="B3257" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3257" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="inlineStr">
+        <is>
+          <t>CVE-2025-24200</t>
+        </is>
+      </c>
+      <c r="B3258" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3258" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" t="inlineStr">
+        <is>
+          <t>CVE-2025-20701</t>
+        </is>
+      </c>
+      <c r="B3259" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3259" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="inlineStr">
+        <is>
+          <t>CVE-2025-43529</t>
+        </is>
+      </c>
+      <c r="B3260" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3260" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="inlineStr">
+        <is>
+          <t>CVE-2025-14174</t>
+        </is>
+      </c>
+      <c r="B3261" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3261" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="inlineStr">
+        <is>
+          <t>CVE-2025-31201</t>
+        </is>
+      </c>
+      <c r="B3262" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3262" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="inlineStr">
+        <is>
+          <t>CVE-2025-24201</t>
+        </is>
+      </c>
+      <c r="B3263" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3263" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="inlineStr">
+        <is>
+          <t>CVE-2025-24085</t>
+        </is>
+      </c>
+      <c r="B3264" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3264" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" t="inlineStr">
+        <is>
+          <t>CVE-2026-20700</t>
+        </is>
+      </c>
+      <c r="B3265" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3265" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3265"/>
+  <dimension ref="A1:C3266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55921,6 +55921,23 @@
         </is>
       </c>
     </row>
+    <row r="3266">
+      <c r="A3266" t="inlineStr">
+        <is>
+          <t>CVE-2026-86950</t>
+        </is>
+      </c>
+      <c r="B3266" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3266" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/apple-patches-coregraphics-zero-day-flaw-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3266"/>
+  <dimension ref="A1:C3268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55938,6 +55938,40 @@
         </is>
       </c>
     </row>
+    <row r="3267">
+      <c r="A3267" t="inlineStr">
+        <is>
+          <t>CVE-2026-64508</t>
+        </is>
+      </c>
+      <c r="B3267" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3267" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-spectre-v2-attack-variant-leaks-linux-root-password-hash-in-minutes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="inlineStr">
+        <is>
+          <t>CVE-2026-64507</t>
+        </is>
+      </c>
+      <c r="B3268" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3268" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-spectre-v2-attack-variant-leaks-linux-root-password-hash-in-minutes/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3268"/>
+  <dimension ref="A1:C3270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55972,6 +55972,40 @@
         </is>
       </c>
     </row>
+    <row r="3269">
+      <c r="A3269" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3269" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3269" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-exploit-citrix-netscaler-zero-day-to-deploy-web-shells/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3270" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3270" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-exploit-citrix-netscaler-zero-day-to-deploy-web-shells/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3270"/>
+  <dimension ref="A1:C3275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56006,6 +56006,91 @@
         </is>
       </c>
     </row>
+    <row r="3271">
+      <c r="A3271" t="inlineStr">
+        <is>
+          <t>CVE-2026-19743</t>
+        </is>
+      </c>
+      <c r="B3271" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3271" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/teamviewer-urges-users-to-patch-severe-flaws-as-soon-as-possible/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="inlineStr">
+        <is>
+          <t>CVE-2026-92369</t>
+        </is>
+      </c>
+      <c r="B3272" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3272" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/teamviewer-urges-users-to-patch-severe-flaws-as-soon-as-possible/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="inlineStr">
+        <is>
+          <t>CVE-2026-92368</t>
+        </is>
+      </c>
+      <c r="B3273" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3273" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/teamviewer-urges-users-to-patch-severe-flaws-as-soon-as-possible/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" t="inlineStr">
+        <is>
+          <t>CVE-2026-92370</t>
+        </is>
+      </c>
+      <c r="B3274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3274" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/teamviewer-urges-users-to-patch-severe-flaws-as-soon-as-possible/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="inlineStr">
+        <is>
+          <t>CVE-2026-92371</t>
+        </is>
+      </c>
+      <c r="B3275" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3275" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/teamviewer-urges-users-to-patch-severe-flaws-as-soon-as-possible/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3275"/>
+  <dimension ref="A1:C3280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56091,6 +56091,91 @@
         </is>
       </c>
     </row>
+    <row r="3276">
+      <c r="A3276" t="inlineStr">
+        <is>
+          <t>CVE-2026-76504</t>
+        </is>
+      </c>
+      <c r="B3276" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3276" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-new-sd-wan-authentication-bypass-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="inlineStr">
+        <is>
+          <t>CVE-2026-20182</t>
+        </is>
+      </c>
+      <c r="B3277" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3277" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-new-sd-wan-authentication-bypass-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="inlineStr">
+        <is>
+          <t>CVE-2026-20245</t>
+        </is>
+      </c>
+      <c r="B3278" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3278" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-new-sd-wan-authentication-bypass-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="inlineStr">
+        <is>
+          <t>CVE-2026-20262</t>
+        </is>
+      </c>
+      <c r="B3279" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3279" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-new-sd-wan-authentication-bypass-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="inlineStr">
+        <is>
+          <t>CVE-2026-20127</t>
+        </is>
+      </c>
+      <c r="B3280" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3280" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-new-sd-wan-authentication-bypass-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3280"/>
+  <dimension ref="A1:C3283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56176,6 +56176,57 @@
         </is>
       </c>
     </row>
+    <row r="3281">
+      <c r="A3281" t="inlineStr">
+        <is>
+          <t>CVE-2026-84411</t>
+        </is>
+      </c>
+      <c r="B3281" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3281" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-critical-pre-auth-rce-flaw-in-mikrotik-routeros/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="inlineStr">
+        <is>
+          <t>CVE-2026-86060</t>
+        </is>
+      </c>
+      <c r="B3282" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3282" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-critical-pre-auth-rce-flaw-in-mikrotik-routeros/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="inlineStr">
+        <is>
+          <t>CVE-2026-67276</t>
+        </is>
+      </c>
+      <c r="B3283" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3283" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisa-warns-of-critical-pre-auth-rce-flaw-in-mikrotik-routeros/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3283"/>
+  <dimension ref="A1:C3285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56227,6 +56227,40 @@
         </is>
       </c>
     </row>
+    <row r="3284">
+      <c r="A3284" t="inlineStr">
+        <is>
+          <t>CVE-2026-102489</t>
+        </is>
+      </c>
+      <c r="B3284" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3284" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/divd-says-zammad-zero-days-enabled-ai-driven-network-breach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" t="inlineStr">
+        <is>
+          <t>CVE-2026-102490</t>
+        </is>
+      </c>
+      <c r="B3285" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3285" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/divd-says-zammad-zero-days-enabled-ai-driven-network-breach/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3285"/>
+  <dimension ref="A1:C3286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56261,6 +56261,23 @@
         </is>
       </c>
     </row>
+    <row r="3286">
+      <c r="A3286" t="inlineStr">
+        <is>
+          <t>CVE-2026-54154</t>
+        </is>
+      </c>
+      <c r="B3286" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3286" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/kiteworks-patches-max-severity-email-protection-gateway-code-injection-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3286"/>
+  <dimension ref="A1:C3287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56278,6 +56278,23 @@
         </is>
       </c>
     </row>
+    <row r="3287">
+      <c r="A3287" t="inlineStr">
+        <is>
+          <t>CVE-2026-104286</t>
+        </is>
+      </c>
+      <c r="B3287" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3287" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fortinet-warns-of-critical-fortimail-flaw-exploited-in-zero-day-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3287"/>
+  <dimension ref="A1:C3295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56295,6 +56295,142 @@
         </is>
       </c>
     </row>
+    <row r="3288">
+      <c r="A3288" t="inlineStr">
+        <is>
+          <t>CVE-2026-54472</t>
+        </is>
+      </c>
+      <c r="B3288" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3288" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="inlineStr">
+        <is>
+          <t>CVE-2026-63692</t>
+        </is>
+      </c>
+      <c r="B3289" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3289" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" t="inlineStr">
+        <is>
+          <t>CVE-2026-67269</t>
+        </is>
+      </c>
+      <c r="B3290" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3290" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="inlineStr">
+        <is>
+          <t>CVE-2021-21551</t>
+        </is>
+      </c>
+      <c r="B3291" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3291" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="inlineStr">
+        <is>
+          <t>CVE-2026-22769</t>
+        </is>
+      </c>
+      <c r="B3292" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3292" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="inlineStr">
+        <is>
+          <t>CVE-2026-61421</t>
+        </is>
+      </c>
+      <c r="B3293" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3293" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="inlineStr">
+        <is>
+          <t>CVE-2026-63688</t>
+        </is>
+      </c>
+      <c r="B3294" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3294" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="inlineStr">
+        <is>
+          <t>CVE-2026-67273</t>
+        </is>
+      </c>
+      <c r="B3295" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3295" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-max-severity-dell-csm-flaws-give-hackers-admin-privileges/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3295"/>
+  <dimension ref="A1:C3297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56431,6 +56431,40 @@
         </is>
       </c>
     </row>
+    <row r="3296">
+      <c r="A3296" t="inlineStr">
+        <is>
+          <t>CVE-2026-90970</t>
+        </is>
+      </c>
+      <c r="B3296" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3296" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/gitlab-warns-of-critical-rce-vulnerability-in-ai-gateway-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="inlineStr">
+        <is>
+          <t>CVE-2026-85706</t>
+        </is>
+      </c>
+      <c r="B3297" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3297" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/gitlab-warns-of-critical-rce-vulnerability-in-ai-gateway-service/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3297"/>
+  <dimension ref="A1:C3302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56465,6 +56465,91 @@
         </is>
       </c>
     </row>
+    <row r="3298">
+      <c r="A3298" t="inlineStr">
+        <is>
+          <t>CVE-2025-49704</t>
+        </is>
+      </c>
+      <c r="B3298" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3298" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/warlock-ransomware-breach-sharepoint-in-water-telecom-operator-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="inlineStr">
+        <is>
+          <t>CVE-2025-1055</t>
+        </is>
+      </c>
+      <c r="B3299" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3299" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/warlock-ransomware-breach-sharepoint-in-water-telecom-operator-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="inlineStr">
+        <is>
+          <t>CVE-2025-53770</t>
+        </is>
+      </c>
+      <c r="B3300" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3300" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/warlock-ransomware-breach-sharepoint-in-water-telecom-operator-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="inlineStr">
+        <is>
+          <t>CVE-2025-53771</t>
+        </is>
+      </c>
+      <c r="B3301" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3301" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/warlock-ransomware-breach-sharepoint-in-water-telecom-operator-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="inlineStr">
+        <is>
+          <t>CVE-2025-49706</t>
+        </is>
+      </c>
+      <c r="B3302" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3302" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/warlock-ransomware-breach-sharepoint-in-water-telecom-operator-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3302"/>
+  <dimension ref="A1:C3306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56550,6 +56550,74 @@
         </is>
       </c>
     </row>
+    <row r="3303">
+      <c r="A3303" t="inlineStr">
+        <is>
+          <t>CVE-2025-6543</t>
+        </is>
+      </c>
+      <c r="B3303" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C3303" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-patches-netscaler-saml-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3304" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C3304" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-patches-netscaler-saml-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="inlineStr">
+        <is>
+          <t>CVE-2026-88778</t>
+        </is>
+      </c>
+      <c r="B3305" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C3305" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-patches-netscaler-saml-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="inlineStr">
+        <is>
+          <t>CVE-2026-88779</t>
+        </is>
+      </c>
+      <c r="B3306" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C3306" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-patches-netscaler-saml-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3306"/>
+  <dimension ref="A1:C3315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56618,6 +56618,159 @@
         </is>
       </c>
     </row>
+    <row r="3307">
+      <c r="A3307" t="inlineStr">
+        <is>
+          <t>CVE-2026-86361</t>
+        </is>
+      </c>
+      <c r="B3307" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3307" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="inlineStr">
+        <is>
+          <t>CVE-2026-22769</t>
+        </is>
+      </c>
+      <c r="B3308" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3308" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="inlineStr">
+        <is>
+          <t>CVE-2026-86360</t>
+        </is>
+      </c>
+      <c r="B3309" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3309" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="inlineStr">
+        <is>
+          <t>CVE-2026-86362</t>
+        </is>
+      </c>
+      <c r="B3310" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3310" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="inlineStr">
+        <is>
+          <t>CVE-2026-63697</t>
+        </is>
+      </c>
+      <c r="B3311" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3311" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="inlineStr">
+        <is>
+          <t>CVE-2026-71168</t>
+        </is>
+      </c>
+      <c r="B3312" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3312" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="inlineStr">
+        <is>
+          <t>CVE-2026-63692</t>
+        </is>
+      </c>
+      <c r="B3313" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3313" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" t="inlineStr">
+        <is>
+          <t>CVE-2026-63688</t>
+        </is>
+      </c>
+      <c r="B3314" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3314" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="inlineStr">
+        <is>
+          <t>CVE-2021-21551</t>
+        </is>
+      </c>
+      <c r="B3315" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3315" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/new-dell-system-update-flaw-lets-hackers-gain-root-privileges/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3315"/>
+  <dimension ref="A1:C3316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56771,6 +56771,23 @@
         </is>
       </c>
     </row>
+    <row r="3316">
+      <c r="A3316" t="inlineStr">
+        <is>
+          <t>CVE-2026-61500</t>
+        </is>
+      </c>
+      <c r="B3316" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3316" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/rejetto-hfs-servers-now-actively-scanned-for-critical-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3316"/>
+  <dimension ref="A1:C3319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56788,6 +56788,57 @@
         </is>
       </c>
     </row>
+    <row r="3317">
+      <c r="A3317" t="inlineStr">
+        <is>
+          <t>CVE-2025-53771</t>
+        </is>
+      </c>
+      <c r="B3317" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3317" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/how-to-secure-rmm-software-8-controls-msps-should-test/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="inlineStr">
+        <is>
+          <t>CVE-2025-53770</t>
+        </is>
+      </c>
+      <c r="B3318" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3318" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/how-to-secure-rmm-software-8-controls-msps-should-test/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="inlineStr">
+        <is>
+          <t>CVE-2026-86218</t>
+        </is>
+      </c>
+      <c r="B3319" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3319" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/how-to-secure-rmm-software-8-controls-msps-should-test/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3319"/>
+  <dimension ref="A1:C3320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56839,6 +56839,23 @@
         </is>
       </c>
     </row>
+    <row r="3320">
+      <c r="A3320" t="inlineStr">
+        <is>
+          <t>CVE-2026-21589</t>
+        </is>
+      </c>
+      <c r="B3320" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3320" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/atlassian-warns-of-critical-file-access-flaw-in-jira-confluence/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3320"/>
+  <dimension ref="A1:C3322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56856,6 +56856,40 @@
         </is>
       </c>
     </row>
+    <row r="3321">
+      <c r="A3321" t="inlineStr">
+        <is>
+          <t>CVE-2026-94504</t>
+        </is>
+      </c>
+      <c r="B3321" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3321" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ninja-forms-plugin-flaw-exploited-to-hack-wordpress-sites/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="inlineStr">
+        <is>
+          <t>CVE-2026-93836</t>
+        </is>
+      </c>
+      <c r="B3322" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3322" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ninja-forms-plugin-flaw-exploited-to-hack-wordpress-sites/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3322"/>
+  <dimension ref="A1:C3327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56890,6 +56890,91 @@
         </is>
       </c>
     </row>
+    <row r="3323">
+      <c r="A3323" t="inlineStr">
+        <is>
+          <t>CVE-2026-15409</t>
+        </is>
+      </c>
+      <c r="B3323" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3323" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sonicwall-warns-of-max-severity-ssrf-flaw-in-sma1000-gateways/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="inlineStr">
+        <is>
+          <t>CVE-2026-83548</t>
+        </is>
+      </c>
+      <c r="B3324" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3324" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sonicwall-warns-of-max-severity-ssrf-flaw-in-sma1000-gateways/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="inlineStr">
+        <is>
+          <t>CVE-2026-83549</t>
+        </is>
+      </c>
+      <c r="B3325" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3325" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sonicwall-warns-of-max-severity-ssrf-flaw-in-sma1000-gateways/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="inlineStr">
+        <is>
+          <t>CVE-2026-15410</t>
+        </is>
+      </c>
+      <c r="B3326" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3326" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sonicwall-warns-of-max-severity-ssrf-flaw-in-sma1000-gateways/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="inlineStr">
+        <is>
+          <t>CVE-2026-102255</t>
+        </is>
+      </c>
+      <c r="B3327" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3327" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sonicwall-warns-of-max-severity-ssrf-flaw-in-sma1000-gateways/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3327"/>
+  <dimension ref="A1:C3328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56975,6 +56975,23 @@
         </is>
       </c>
     </row>
+    <row r="3328">
+      <c r="A3328" t="inlineStr">
+        <is>
+          <t>CVE-2026-21589</t>
+        </is>
+      </c>
+      <c r="B3328" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3328" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/hackers-exploit-critical-atlassian-flaw-after-public-poc-release/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3328"/>
+  <dimension ref="A1:C3330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56992,6 +56992,40 @@
         </is>
       </c>
     </row>
+    <row r="3329">
+      <c r="A3329" t="inlineStr">
+        <is>
+          <t>CVE-2026-48710</t>
+        </is>
+      </c>
+      <c r="B3329" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3329" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/poellm-malware-infects-exposed-ai-servers-in-cryptomining-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="inlineStr">
+        <is>
+          <t>CVE-2026-42271</t>
+        </is>
+      </c>
+      <c r="B3330" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3330" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/poellm-malware-infects-exposed-ai-servers-in-cryptomining-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3330"/>
+  <dimension ref="A1:C3339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57026,6 +57026,159 @@
         </is>
       </c>
     </row>
+    <row r="3331">
+      <c r="A3331" t="inlineStr">
+        <is>
+          <t>CVE-2026-76484</t>
+        </is>
+      </c>
+      <c r="B3331" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3331" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="inlineStr">
+        <is>
+          <t>CVE-2026-76465</t>
+        </is>
+      </c>
+      <c r="B3332" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3332" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="inlineStr">
+        <is>
+          <t>CVE-2026-76486</t>
+        </is>
+      </c>
+      <c r="B3333" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3333" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="inlineStr">
+        <is>
+          <t>CVE-2026-76483</t>
+        </is>
+      </c>
+      <c r="B3334" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3334" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="inlineStr">
+        <is>
+          <t>CVE-2026-76471</t>
+        </is>
+      </c>
+      <c r="B3335" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3335" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="inlineStr">
+        <is>
+          <t>CVE-2026-76485</t>
+        </is>
+      </c>
+      <c r="B3336" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3336" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="inlineStr">
+        <is>
+          <t>CVE-2026-76482</t>
+        </is>
+      </c>
+      <c r="B3337" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3337" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="inlineStr">
+        <is>
+          <t>CVE-2026-76501</t>
+        </is>
+      </c>
+      <c r="B3338" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3338" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="inlineStr">
+        <is>
+          <t>CVE-2026-76480</t>
+        </is>
+      </c>
+      <c r="B3339" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3339" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cisco-warns-of-critical-flaws-allowing-nexus-switch-takeover/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3339"/>
+  <dimension ref="A1:C3347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57179,6 +57179,142 @@
         </is>
       </c>
     </row>
+    <row r="3340">
+      <c r="A3340" t="inlineStr">
+        <is>
+          <t>CVE-2019-11510</t>
+        </is>
+      </c>
+      <c r="B3340" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3340" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="inlineStr">
+        <is>
+          <t>CVE-2021-3199</t>
+        </is>
+      </c>
+      <c r="B3341" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3341" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="inlineStr">
+        <is>
+          <t>CVE-2016-3081</t>
+        </is>
+      </c>
+      <c r="B3342" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3342" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="inlineStr">
+        <is>
+          <t>CVE-2014-6278</t>
+        </is>
+      </c>
+      <c r="B3343" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3343" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="inlineStr">
+        <is>
+          <t>CVE-2015-3306</t>
+        </is>
+      </c>
+      <c r="B3344" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3344" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="inlineStr">
+        <is>
+          <t>CVE-2021-22205</t>
+        </is>
+      </c>
+      <c r="B3345" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3345" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="inlineStr">
+        <is>
+          <t>CVE-2023-22894</t>
+        </is>
+      </c>
+      <c r="B3346" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3346" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="inlineStr">
+        <is>
+          <t>CVE-2015-5477</t>
+        </is>
+      </c>
+      <c r="B3347" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3347" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/fbi-disrupts-chinese-hacking-tools-used-to-breach-critical-infrastructure/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3347"/>
+  <dimension ref="A1:C3353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57315,6 +57315,108 @@
         </is>
       </c>
     </row>
+    <row r="3348">
+      <c r="A3348" t="inlineStr">
+        <is>
+          <t>CVE-2026-88779</t>
+        </is>
+      </c>
+      <c r="B3348" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3348" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="inlineStr">
+        <is>
+          <t>CVE-2026-4368</t>
+        </is>
+      </c>
+      <c r="B3349" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3349" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3350" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3350" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="inlineStr">
+        <is>
+          <t>CVE-2026-107406</t>
+        </is>
+      </c>
+      <c r="B3351" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3351" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3352" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3352" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="inlineStr">
+        <is>
+          <t>CVE-2026-3055</t>
+        </is>
+      </c>
+      <c r="B3353" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3353" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/citrix-warns-admins-to-patch-new-netscaler-rce-flaw-immediately/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3353"/>
+  <dimension ref="A1:C3358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57417,6 +57417,91 @@
         </is>
       </c>
     </row>
+    <row r="3354">
+      <c r="A3354" t="inlineStr">
+        <is>
+          <t>CVE-2026-15409</t>
+        </is>
+      </c>
+      <c r="B3354" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3354" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/max-severity-sonicwall-sma1000-flaw-now-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="inlineStr">
+        <is>
+          <t>CVE-2026-83549</t>
+        </is>
+      </c>
+      <c r="B3355" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3355" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/max-severity-sonicwall-sma1000-flaw-now-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="inlineStr">
+        <is>
+          <t>CVE-2026-83548</t>
+        </is>
+      </c>
+      <c r="B3356" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3356" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/max-severity-sonicwall-sma1000-flaw-now-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="inlineStr">
+        <is>
+          <t>CVE-2026-102255</t>
+        </is>
+      </c>
+      <c r="B3357" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3357" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/max-severity-sonicwall-sma1000-flaw-now-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="inlineStr">
+        <is>
+          <t>CVE-2026-15410</t>
+        </is>
+      </c>
+      <c r="B3358" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3358" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/max-severity-sonicwall-sma1000-flaw-now-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3358"/>
+  <dimension ref="A1:C3360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57502,6 +57502,40 @@
         </is>
       </c>
     </row>
+    <row r="3359">
+      <c r="A3359" t="inlineStr">
+        <is>
+          <t>CVE-2026-105134</t>
+        </is>
+      </c>
+      <c r="B3359" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3359" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/unpatched-ahsaycbs-flaws-exploited-to-deploy-webshells-mine-crypto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="inlineStr">
+        <is>
+          <t>CVE-2026-105133</t>
+        </is>
+      </c>
+      <c r="B3360" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3360" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/unpatched-ahsaycbs-flaws-exploited-to-deploy-webshells-mine-crypto/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3360"/>
+  <dimension ref="A1:C3363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57536,6 +57536,57 @@
         </is>
       </c>
     </row>
+    <row r="3361">
+      <c r="A3361" t="inlineStr">
+        <is>
+          <t>CVE-2026-85706</t>
+        </is>
+      </c>
+      <c r="B3361" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3361" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/gitlab-warns-of-max-severity-rce-flaw-in-regex-compiler-engine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" t="inlineStr">
+        <is>
+          <t>CVE-2026-0723</t>
+        </is>
+      </c>
+      <c r="B3362" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3362" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/gitlab-warns-of-max-severity-rce-flaw-in-regex-compiler-engine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="inlineStr">
+        <is>
+          <t>CVE-2026-97229</t>
+        </is>
+      </c>
+      <c r="B3363" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3363" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/gitlab-warns-of-max-severity-rce-flaw-in-regex-compiler-engine/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3363"/>
+  <dimension ref="A1:C3364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57587,6 +57587,23 @@
         </is>
       </c>
     </row>
+    <row r="3364">
+      <c r="A3364" t="inlineStr">
+        <is>
+          <t>CVE-2025-41450</t>
+        </is>
+      </c>
+      <c r="B3364" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3364" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cyberattack-shuts-down-refrigerators-at-french-supermarkets/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3364"/>
+  <dimension ref="A1:C3365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57604,6 +57604,23 @@
         </is>
       </c>
     </row>
+    <row r="3365">
+      <c r="A3365" t="inlineStr">
+        <is>
+          <t>CVE-2025-41451</t>
+        </is>
+      </c>
+      <c r="B3365" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3365" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/cyberattack-shuts-down-refrigerators-at-french-supermarkets/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3365"/>
+  <dimension ref="A1:C3370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57621,6 +57621,91 @@
         </is>
       </c>
     </row>
+    <row r="3366">
+      <c r="A3366" t="inlineStr">
+        <is>
+          <t>CVE-2026-58231</t>
+        </is>
+      </c>
+      <c r="B3366" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3366" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sap-warns-of-maximum-severity-oauth2-ssrf-security-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="inlineStr">
+        <is>
+          <t>CVE-2026-89111</t>
+        </is>
+      </c>
+      <c r="B3367" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3367" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sap-warns-of-maximum-severity-oauth2-ssrf-security-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="inlineStr">
+        <is>
+          <t>CVE-2026-44756</t>
+        </is>
+      </c>
+      <c r="B3368" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3368" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sap-warns-of-maximum-severity-oauth2-ssrf-security-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="inlineStr">
+        <is>
+          <t>CVE-2026-89108</t>
+        </is>
+      </c>
+      <c r="B3369" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3369" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sap-warns-of-maximum-severity-oauth2-ssrf-security-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="inlineStr">
+        <is>
+          <t>CVE-2026-89110</t>
+        </is>
+      </c>
+      <c r="B3370" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3370" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/sap-warns-of-maximum-severity-oauth2-ssrf-security-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3370"/>
+  <dimension ref="A1:C3376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57706,6 +57706,108 @@
         </is>
       </c>
     </row>
+    <row r="3371">
+      <c r="A3371" t="inlineStr">
+        <is>
+          <t>CVE-2023-46805</t>
+        </is>
+      </c>
+      <c r="B3371" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3371" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" t="inlineStr">
+        <is>
+          <t>CVE-2024-21887</t>
+        </is>
+      </c>
+      <c r="B3372" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3372" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="inlineStr">
+        <is>
+          <t>CVE-2024-21893</t>
+        </is>
+      </c>
+      <c r="B3373" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3373" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="inlineStr">
+        <is>
+          <t>CVE-2025-0282</t>
+        </is>
+      </c>
+      <c r="B3374" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3374" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="inlineStr">
+        <is>
+          <t>CVE-2025-22457</t>
+        </is>
+      </c>
+      <c r="B3375" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3375" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="inlineStr">
+        <is>
+          <t>CVE-2026-104935</t>
+        </is>
+      </c>
+      <c r="B3376" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3376" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/ivanti-warns-of-connect-secure-zero-day-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3376"/>
+  <dimension ref="A1:C3377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57808,6 +57808,23 @@
         </is>
       </c>
     </row>
+    <row r="3377">
+      <c r="A3377" t="inlineStr">
+        <is>
+          <t>CVE-2026-105445</t>
+        </is>
+      </c>
+      <c r="B3377" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3377" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/docker-hub-flaw-let-attackers-impersonate-users-tamper-with-images/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
